--- a/docs/テーブル構造.xlsx
+++ b/docs/テーブル構造.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUNABACO\inv_mgmt\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC640B99-D0FD-45AF-8FCD-81FADF4D8DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D240A-734B-4B52-88E7-B92F6EEB71BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6162" yWindow="0" windowWidth="14874" windowHeight="12240" xr2:uid="{48C7D2FB-9341-4D8A-95BC-D73F79E9D314}"/>
+    <workbookView xWindow="516" yWindow="0" windowWidth="14874" windowHeight="12240" xr2:uid="{48C7D2FB-9341-4D8A-95BC-D73F79E9D314}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
+    <sheet name="ER" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="54">
   <si>
     <t>テーブル名</t>
     <rPh sb="4" eb="5">
@@ -279,17 +280,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>T_入出庫</t>
-    <rPh sb="2" eb="5">
-      <t>ニュウシュッコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>t_inout</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シーケンシャルNO</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -356,13 +346,27 @@
       <t>チョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TD_入出庫</t>
+    <rPh sb="3" eb="6">
+      <t>ニュウシュッコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>td_inout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>🔑</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,8 +389,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,8 +409,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -423,13 +445,133 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -442,14 +584,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,127 +1000,127 @@
   <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="17.7" x14ac:dyDescent="0.85"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4" t="s">
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4" t="s">
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A4" s="1">
@@ -1140,127 +1348,127 @@
       <c r="AE8" s="3"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4" t="s">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4" t="s">
+      <c r="L12" s="5"/>
+      <c r="M12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4" t="s">
+      <c r="N12" s="5"/>
+      <c r="O12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4" t="s">
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4" t="s">
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A13" s="1">
@@ -1382,7 +1590,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -1470,7 +1678,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -1570,140 +1778,140 @@
       <c r="AE19" s="3"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
-      <c r="AB22" s="4"/>
-      <c r="AC22" s="4"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4" t="s">
+      <c r="L23" s="5"/>
+      <c r="M23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
+      <c r="N23" s="5"/>
+      <c r="O23" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4" t="s">
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4" t="s">
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A24" s="1">
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1729,7 +1937,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
@@ -1778,7 +1986,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
@@ -1795,13 +2003,13 @@
         <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1826,31 +2034,31 @@
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
-      <c r="V26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
-      <c r="AB26" s="6"/>
-      <c r="AC26" s="6"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
+      <c r="V26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A27" s="1">
         <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1869,7 +2077,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -2140,4 +2348,617 @@
   <pageMargins left="0.59055118110236215" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5DB53D-2E82-4EC8-92DD-FFDFF433DE79}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:AN22"/>
+  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="17.7" x14ac:dyDescent="0.85"/>
+  <cols>
+    <col min="2" max="2" width="3.37890625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.37890625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.5234375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.37890625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="3.5234375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:40" ht="18" thickBot="1" x14ac:dyDescent="0.9"/>
+    <row r="3" spans="2:40" ht="18" thickTop="1" x14ac:dyDescent="0.85">
+      <c r="B3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9"/>
+      <c r="AD3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="9"/>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="19"/>
+      <c r="AD4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="11"/>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="13"/>
+      <c r="AD5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="13"/>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B6" s="21">
+        <v>1</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="AD6" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B7" s="14">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="15"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="27"/>
+      <c r="AD7" s="21">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF7" s="22"/>
+      <c r="AG7" s="22"/>
+      <c r="AH7" s="22"/>
+      <c r="AI7" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ7" s="22"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="22"/>
+      <c r="AM7" s="22"/>
+      <c r="AN7" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B8" s="14">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="15"/>
+      <c r="AD8" s="14">
+        <v>3</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B9" s="14">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="15"/>
+      <c r="AD9" s="14">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="15"/>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="B10" s="14">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="15"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="24">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="25"/>
+      <c r="AM10" s="25"/>
+      <c r="AN10" s="26"/>
+    </row>
+    <row r="11" spans="2:40" ht="18" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B11" s="24">
+        <v>6</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="AB11" s="28"/>
+      <c r="AD11" s="16">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="18"/>
+    </row>
+    <row r="12" spans="2:40" ht="18.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B12" s="16">
+        <v>7</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="N12" s="28"/>
+      <c r="AB12" s="28"/>
+    </row>
+    <row r="13" spans="2:40" ht="18.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="N13" s="28"/>
+      <c r="AB13" s="28"/>
+    </row>
+    <row r="14" spans="2:40" ht="18" thickTop="1" x14ac:dyDescent="0.85">
+      <c r="N14" s="28"/>
+      <c r="P14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="9"/>
+      <c r="AB14" s="28"/>
+    </row>
+    <row r="15" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="N15" s="28"/>
+      <c r="P15" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="11"/>
+      <c r="AB15" s="28"/>
+    </row>
+    <row r="16" spans="2:40" x14ac:dyDescent="0.85">
+      <c r="N16" s="28"/>
+      <c r="P16" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="20"/>
+      <c r="AB16" s="28"/>
+    </row>
+    <row r="17" spans="14:28" x14ac:dyDescent="0.85">
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+    </row>
+    <row r="18" spans="14:28" x14ac:dyDescent="0.85">
+      <c r="P18" s="14">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="15"/>
+    </row>
+    <row r="19" spans="14:28" x14ac:dyDescent="0.85">
+      <c r="P19" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="15"/>
+    </row>
+    <row r="20" spans="14:28" x14ac:dyDescent="0.85">
+      <c r="P20" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="15"/>
+    </row>
+    <row r="21" spans="14:28" ht="18" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="P21" s="16">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="18"/>
+    </row>
+    <row r="22" spans="14:28" ht="18" thickTop="1" x14ac:dyDescent="0.85"/>
+  </sheetData>
+  <mergeCells count="54">
+    <mergeCell ref="AE11:AH11"/>
+    <mergeCell ref="AI11:AM11"/>
+    <mergeCell ref="AE10:AH10"/>
+    <mergeCell ref="AI10:AM10"/>
+    <mergeCell ref="AE9:AH9"/>
+    <mergeCell ref="AI9:AM9"/>
+    <mergeCell ref="AE8:AH8"/>
+    <mergeCell ref="AI8:AM8"/>
+    <mergeCell ref="AE7:AH7"/>
+    <mergeCell ref="AI7:AM7"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="AI6:AM6"/>
+    <mergeCell ref="AD3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AE5:AH5"/>
+    <mergeCell ref="AI5:AM5"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="U21:Y21"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="U20:Y20"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="U19:Y19"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:Y18"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="U17:Y17"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="V14:Z14"/>
+    <mergeCell ref="P15:U15"/>
+    <mergeCell ref="V15:Z15"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U16:Y16"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.59055118110236215" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/テーブル構造.xlsx
+++ b/docs/テーブル構造.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUNABACO\inv_mgmt\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D240A-734B-4B52-88E7-B92F6EEB71BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51042CD4-EB9E-46F4-BE43-8E90D1F3522B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="516" yWindow="0" windowWidth="14874" windowHeight="12240" xr2:uid="{48C7D2FB-9341-4D8A-95BC-D73F79E9D314}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{48C7D2FB-9341-4D8A-95BC-D73F79E9D314}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="55">
   <si>
     <t>テーブル名</t>
     <rPh sb="4" eb="5">
@@ -360,6 +360,10 @@
   </si>
   <si>
     <t>🔑</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -581,16 +585,64 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -608,56 +660,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1000,1328 +1004,1190 @@
   <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="17.7" x14ac:dyDescent="0.85"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="16"/>
+      <c r="M3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
+      <c r="N3" s="16"/>
+      <c r="O3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5" t="s">
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5" t="s">
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3" t="s">
+      <c r="N4" s="17"/>
+      <c r="O4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3">
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17">
         <v>4</v>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3" t="s">
+      <c r="N5" s="17"/>
+      <c r="O5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3">
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17">
         <v>10</v>
       </c>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3" t="s">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3">
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17">
         <v>1</v>
       </c>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3" t="s">
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3">
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17">
         <v>10</v>
       </c>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3" t="s">
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6" t="s">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5" t="s">
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5" t="s">
+      <c r="L12" s="16"/>
+      <c r="M12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5" t="s">
+      <c r="N12" s="16"/>
+      <c r="O12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5" t="s">
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5" t="s">
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A13" s="1">
         <v>1</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3" t="s">
+      <c r="L13" s="17"/>
+      <c r="M13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3" t="s">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3">
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17">
         <v>4</v>
       </c>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3" t="s">
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="17"/>
+      <c r="O14" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3">
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17">
         <v>250</v>
       </c>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3" t="s">
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3" t="s">
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3" t="s">
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A16" s="1">
         <v>4</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3" t="s">
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3">
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17">
         <v>10</v>
       </c>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3" t="s">
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3" t="s">
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A18" s="1">
         <v>6</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3" t="s">
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3">
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17">
         <v>4</v>
       </c>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A19" s="1">
         <v>7</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3" t="s">
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.85">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5" t="s">
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
+      <c r="L23" s="16"/>
+      <c r="M23" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5" t="s">
+      <c r="N23" s="16"/>
+      <c r="O23" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5" t="s">
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5" t="s">
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="5"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="16"/>
+      <c r="AB23" s="16"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="16"/>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A24" s="1">
         <v>1</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3" t="s">
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3" t="s">
+      <c r="L24" s="17"/>
+      <c r="M24" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3" t="s">
+      <c r="N24" s="17"/>
+      <c r="O24" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3">
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17">
         <v>8</v>
       </c>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3" t="s">
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A25" s="1">
         <v>2</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3" t="s">
+      <c r="L25" s="17"/>
+      <c r="M25" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3" t="s">
+      <c r="N25" s="17"/>
+      <c r="O25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3">
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17">
         <v>4</v>
       </c>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3" t="s">
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+      <c r="AC25" s="17"/>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A26" s="1">
         <v>3</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3" t="s">
+      <c r="L26" s="17"/>
+      <c r="M26" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3" t="s">
+      <c r="N26" s="17"/>
+      <c r="O26" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3">
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17">
         <v>1</v>
       </c>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="4" t="s">
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="19"/>
+      <c r="AC26" s="19"/>
+      <c r="AD26" s="19"/>
+      <c r="AE26" s="19"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A27" s="1">
         <v>4</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3" t="s">
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3" t="s">
+      <c r="N27" s="17"/>
+      <c r="O27" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3" t="s">
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3" t="s">
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
+      <c r="AC27" s="17"/>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="17"/>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A28" s="1">
         <v>5</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3" t="s">
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="s">
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3" t="s">
+      <c r="N28" s="17"/>
+      <c r="O28" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3">
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17">
         <v>4</v>
       </c>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
-      <c r="AE28" s="3"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.85">
       <c r="A29" s="1">
         <v>6</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3" t="s">
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3" t="s">
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3" t="s">
+      <c r="N29" s="17"/>
+      <c r="O29" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
-      <c r="AB29" s="3"/>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
-      <c r="AE29" s="3"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="159">
-    <mergeCell ref="V3:AE3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="V4:AE4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:AE1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AE2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="V5:AE5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="V6:AE6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="V7:AE7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="V8:AE8"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:U7"/>
-    <mergeCell ref="V12:AE12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="V13:AE13"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G10:AE10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:AE11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="V14:AE14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="V15:AE15"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="S14:U14"/>
-    <mergeCell ref="V16:AE16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="V17:AE17"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="V18:AE18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="V19:AE19"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="V23:AE23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="V24:AE24"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="G21:AE21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="G22:AE22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="V25:AE25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="V26:AE26"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="S25:U25"/>
     <mergeCell ref="V29:AE29"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="F29:J29"/>
@@ -2343,6 +2209,144 @@
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="S27:U27"/>
+    <mergeCell ref="V25:AE25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="V26:AE26"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="S25:U25"/>
+    <mergeCell ref="V23:AE23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="V24:AE24"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G21:AE21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="G22:AE22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="V18:AE18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="V19:AE19"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="V16:AE16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="V17:AE17"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="V14:AE14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="V15:AE15"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="S14:U14"/>
+    <mergeCell ref="V12:AE12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="V13:AE13"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:AE10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:AE11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="V7:AE7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="V8:AE8"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:U7"/>
+    <mergeCell ref="V5:AE5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="V6:AE6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="V3:AE3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="V4:AE4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:AE1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AE2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:U3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.59055118110236215" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2368,107 +2372,107 @@
   <sheetData>
     <row r="2" spans="2:40" ht="18" thickBot="1" x14ac:dyDescent="0.9"/>
     <row r="3" spans="2:40" ht="18" thickTop="1" x14ac:dyDescent="0.85">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
-      <c r="AD3" s="7" t="s">
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
+      <c r="AD3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8" t="s">
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="8"/>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="9"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="24"/>
+      <c r="AN3" s="25"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6" t="s">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="19"/>
-      <c r="AD4" s="10" t="s">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="28"/>
+      <c r="AD4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5" t="s">
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
-      <c r="AM4" s="5"/>
-      <c r="AN4" s="11"/>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="16"/>
+      <c r="AM4" s="16"/>
+      <c r="AN4" s="27"/>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="13"/>
-      <c r="AD5" s="12" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="3"/>
+      <c r="AD5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AE5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5" t="s">
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
-      <c r="AL5" s="5"/>
-      <c r="AM5" s="5"/>
-      <c r="AN5" s="13"/>
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="16"/>
+      <c r="AM5" s="16"/>
+      <c r="AN5" s="3"/>
     </row>
     <row r="6" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B6" s="21">
+      <c r="B6" s="10">
         <v>1</v>
       </c>
       <c r="C6" s="22" t="s">
@@ -2484,66 +2488,66 @@
       <c r="I6" s="22"/>
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="AD6" s="14">
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="AD6" s="5">
         <v>1</v>
       </c>
-      <c r="AE6" s="3" t="s">
+      <c r="AE6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3" t="s">
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="15" t="s">
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="17"/>
+      <c r="AN6" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B7" s="14">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="15"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="27"/>
-      <c r="AC7" s="27"/>
-      <c r="AD7" s="21">
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="6"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="10">
         <v>2</v>
       </c>
       <c r="AE7" s="22" t="s">
@@ -2559,393 +2563,349 @@
       <c r="AK7" s="22"/>
       <c r="AL7" s="22"/>
       <c r="AM7" s="22"/>
-      <c r="AN7" s="23" t="s">
+      <c r="AN7" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B8" s="14">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="15"/>
-      <c r="AD8" s="14">
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="6"/>
+      <c r="AD8" s="5">
         <v>3</v>
       </c>
-      <c r="AE8" s="3" t="s">
+      <c r="AE8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3" t="s">
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="15" t="s">
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B9" s="14">
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="15"/>
-      <c r="AD9" s="14">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="6"/>
+      <c r="AD9" s="5">
         <v>4</v>
       </c>
-      <c r="AE9" s="3" t="s">
+      <c r="AE9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3" t="s">
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="15"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="6"/>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="B10" s="14">
+      <c r="B10" s="5">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="15"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="24">
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="6"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="12">
         <v>5</v>
       </c>
-      <c r="AE10" s="25" t="s">
+      <c r="AE10" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="25" t="s">
+      <c r="AF10" s="21"/>
+      <c r="AG10" s="21"/>
+      <c r="AH10" s="21"/>
+      <c r="AI10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AJ10" s="25"/>
-      <c r="AK10" s="25"/>
-      <c r="AL10" s="25"/>
-      <c r="AM10" s="25"/>
-      <c r="AN10" s="26"/>
+      <c r="AJ10" s="21"/>
+      <c r="AK10" s="21"/>
+      <c r="AL10" s="21"/>
+      <c r="AM10" s="21"/>
+      <c r="AN10" s="13"/>
     </row>
     <row r="11" spans="2:40" ht="18" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B11" s="24">
+      <c r="B11" s="12">
         <v>6</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="AB11" s="28"/>
-      <c r="AD11" s="16">
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AD11" s="7">
         <v>6</v>
       </c>
-      <c r="AE11" s="17" t="s">
+      <c r="AE11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17" t="s">
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="18"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="8"/>
     </row>
     <row r="12" spans="2:40" ht="18.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B12" s="16">
+      <c r="B12" s="7">
         <v>7</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17" t="s">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="18"/>
-      <c r="N12" s="28"/>
-      <c r="AB12" s="28"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="8"/>
+      <c r="N12" s="15"/>
+      <c r="AB12" s="15"/>
     </row>
     <row r="13" spans="2:40" ht="18.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="N13" s="28"/>
-      <c r="AB13" s="28"/>
+      <c r="N13" s="15"/>
+      <c r="AB13" s="15"/>
     </row>
     <row r="14" spans="2:40" ht="18" thickTop="1" x14ac:dyDescent="0.85">
-      <c r="N14" s="28"/>
-      <c r="P14" s="7" t="s">
+      <c r="N14" s="15"/>
+      <c r="P14" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8" t="s">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="9"/>
-      <c r="AB14" s="28"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="25"/>
+      <c r="AB14" s="15"/>
     </row>
     <row r="15" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="N15" s="28"/>
-      <c r="P15" s="10" t="s">
+      <c r="N15" s="15"/>
+      <c r="P15" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5" t="s">
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="11"/>
-      <c r="AB15" s="28"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="27"/>
+      <c r="AB15" s="15"/>
     </row>
     <row r="16" spans="2:40" x14ac:dyDescent="0.85">
-      <c r="N16" s="28"/>
-      <c r="P16" s="12" t="s">
+      <c r="N16" s="15"/>
+      <c r="P16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Q16" s="5" t="s">
+      <c r="Q16" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5" t="s">
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="20"/>
-      <c r="AB16" s="28"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="9"/>
+      <c r="AB16" s="15"/>
     </row>
     <row r="17" spans="14:28" x14ac:dyDescent="0.85">
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="24">
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="12">
         <v>1</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25" t="s">
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="26" t="s">
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
     </row>
     <row r="18" spans="14:28" x14ac:dyDescent="0.85">
-      <c r="P18" s="14">
+      <c r="P18" s="5">
         <v>2</v>
       </c>
-      <c r="Q18" s="3" t="s">
+      <c r="Q18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3" t="s">
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="15"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="6"/>
     </row>
     <row r="19" spans="14:28" x14ac:dyDescent="0.85">
-      <c r="P19" s="14">
+      <c r="P19" s="5">
         <v>3</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="Q19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3" t="s">
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="15"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="6"/>
     </row>
     <row r="20" spans="14:28" x14ac:dyDescent="0.85">
-      <c r="P20" s="14">
+      <c r="P20" s="5">
         <v>4</v>
       </c>
-      <c r="Q20" s="3" t="s">
+      <c r="Q20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3" t="s">
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="15"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="6"/>
     </row>
     <row r="21" spans="14:28" ht="18" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="P21" s="16">
+      <c r="P21" s="7">
         <v>5</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17" t="s">
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="18"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="8"/>
     </row>
     <row r="22" spans="14:28" ht="18" thickTop="1" x14ac:dyDescent="0.85"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="AE11:AH11"/>
-    <mergeCell ref="AI11:AM11"/>
-    <mergeCell ref="AE10:AH10"/>
-    <mergeCell ref="AI10:AM10"/>
-    <mergeCell ref="AE9:AH9"/>
-    <mergeCell ref="AI9:AM9"/>
-    <mergeCell ref="AE8:AH8"/>
-    <mergeCell ref="AI8:AM8"/>
-    <mergeCell ref="AE7:AH7"/>
-    <mergeCell ref="AI7:AM7"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="AI6:AM6"/>
-    <mergeCell ref="AD3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AE5:AH5"/>
-    <mergeCell ref="AI5:AM5"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="U21:Y21"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="U20:Y20"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="U19:Y19"/>
     <mergeCell ref="Q18:T18"/>
     <mergeCell ref="U18:Y18"/>
     <mergeCell ref="Q17:T17"/>
@@ -2956,6 +2916,50 @@
     <mergeCell ref="V15:Z15"/>
     <mergeCell ref="Q16:T16"/>
     <mergeCell ref="U16:Y16"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="U21:Y21"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="U20:Y20"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="U19:Y19"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="AD3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AE5:AH5"/>
+    <mergeCell ref="AI5:AM5"/>
+    <mergeCell ref="AE8:AH8"/>
+    <mergeCell ref="AI8:AM8"/>
+    <mergeCell ref="AE7:AH7"/>
+    <mergeCell ref="AI7:AM7"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="AI6:AM6"/>
+    <mergeCell ref="AE11:AH11"/>
+    <mergeCell ref="AI11:AM11"/>
+    <mergeCell ref="AE10:AH10"/>
+    <mergeCell ref="AI10:AM10"/>
+    <mergeCell ref="AE9:AH9"/>
+    <mergeCell ref="AI9:AM9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.59055118110236215" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
